--- a/reports/pdf_change_20260923.xlsx
+++ b/reports/pdf_change_20260923.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억   ·   현금 20억(0.4%)      당일 2026-09-23  vs  전영업일 2026-09-22      매수 7종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억      당일 2026-09-23  vs  전영업일 2026-09-22      매수 7종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1027,7 +1027,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억   ·   현금 59억(1.8%)      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1051,7 +1051,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 43억(1.6%)      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1075,7 +1075,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 16억(0.8%)      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억      당일 2026-09-23  vs  전영업일 2026-09-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1099,7 +1099,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 1억(0.4%)      당일 2026-09-23  vs  전영업일 2026-09-22      매수 6종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억      당일 2026-09-23  vs  전영업일 2026-09-22      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>

--- a/reports/pdf_change_20260923.xlsx
+++ b/reports/pdf_change_20260923.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>브이엠  (신규)</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>34</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1909005531</v>
+        <v>954502766</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.40%</t>
+          <t>0.77%→0.99%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→34</t>
+          <t>136→170</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>브이엠  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>34</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>954502766</v>
+        <v>1909005531</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.77%→0.99%</t>
+          <t>0.00%→0.40%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>136→170</t>
+          <t>0→34</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">

--- a/reports/pdf_change_20260923.xlsx
+++ b/reports/pdf_change_20260923.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>브이엠  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>34</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>954502766</v>
+        <v>1909005531</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.77%→0.99%</t>
+          <t>0.00%→0.40%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>136→170</t>
+          <t>0→34</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>브이엠  (신규)</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>34</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1909005531</v>
+        <v>954502766</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.40%</t>
+          <t>0.77%→0.99%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0→34</t>
+          <t>136→170</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
